--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/03_RR3 - Ters PFMEA ve Öğrenilmiş Dersler/EKG-PRJ-PRS-10_ogrenilen_dersler_proseduru_ve_veri_tabani.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/03_RR3 - Ters PFMEA ve Öğrenilmiş Dersler/EKG-PRJ-PRS-10_ogrenilen_dersler_proseduru_ve_veri_tabani.xlsx
@@ -793,7 +793,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-PRS-10&amp;C&amp;"Arial,Regular"&amp;11Öğrenilen Dersler Prosedürü ve Veri Tabanı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.05.2026 | Revizyon: 11.08.2026
+Revizyon nedeni: AP düşüşü varsayımı kaldırıldı; dersin yaygınlaştırma ve etkinliği kanıta bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -946,7 +947,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-PRS-10&amp;C&amp;"Arial,Regular"&amp;11Öğrenilen Dersler Prosedürü ve Veri Tabanı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.05.2026 | Revizyon: 11.08.2026
+Revizyon nedeni: AP düşüşü varsayımı kaldırıldı; dersin yaygınlaştırma ve etkinliği kanıta bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>